--- a/models/data/person.xlsx
+++ b/models/data/person.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A193E8EA-C798-4D33-BE90-4FBA7AF4AA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B52B3D-3BEB-448E-8EA1-95A4A8754D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="1590" windowWidth="22695" windowHeight="13065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29115" yWindow="1515" windowWidth="25905" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="関係者" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">関係者!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">関係者!$A$1:$L$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -118,6 +118,10 @@
   </si>
   <si>
     <t>メモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よみがな</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -530,21 +534,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="5.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="35.25" customWidth="1"/>
-    <col min="10" max="13" width="15.5" customWidth="1"/>
+    <col min="5" max="6" width="22.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.25" customWidth="1"/>
+    <col min="11" max="14" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -561,31 +565,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -593,12 +600,13 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
